--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_032_Argentina.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_032_Argentina.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R666e9c1436684bc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R68390857edea45ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R0253d310d3cf4f4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R41fe50f2d3e7467d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R53f136c62886440e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R2f208714e622406c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R3a9369ebebe04b2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R737f2e5085624f7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re4c3b15974134110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R5a543b149b414293"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9550a69622424cfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R23cffed9a70a4899"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ032CommercialTable" displayName="EEZ032CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ032CommercialTable" displayName="EEZ032CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ032FunctionalTable" displayName="EEZ032FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ032FunctionalTable" displayName="EEZ032FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ032ValidationTable" displayName="EEZ032ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ032ValidationTable" displayName="EEZ032ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6456,7 +6410,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2a6ac23d738420e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b41294d274249eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6466,20 +6420,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6487,552 +6431,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>7768.5010574</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.51</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>32.35936569296281</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>7768.5010574</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>32.35936569296281</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$87,A2,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>251383.76660257488</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.51</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>32.35936569296281</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>251383.76660257488</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>683677.3974355531</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.1401439071631465</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1380.8417424369368</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>683677.3974355531</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1473.7857969223396</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$87,A3,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1007594038.0173478</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.1401439071631465</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1380.8417424369368</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>944050288.7396593</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>63543749.2776885</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0673097080056209</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.06730970800562083</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>286211.68277646</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.2010536481816905</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>15.887429931095472</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>286211.68277646</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>15.898348405205368</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$87,A4,'Species'!$U$2:$U$87))</x:f>
-        <x:v>4550293.050420278</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.2010536481816905</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>15.887429931095472</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>4547168.055571933</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>3124.994848344475</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.00068723979632</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.00068723979632009</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>154.897509167</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.75</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>56.23413251903491</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>154.897509167</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>56.23413251903491</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$87,A5,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>8710.527057365503</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.75</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>56.23413251903491</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>8710.527057365503</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>23992.265780434</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>23992.265780434</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$87,A6,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>239922.65780434</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>239922.65780434</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>329952.03372476954</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.7118071430564346</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>514.9998980365926</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>329952.03372476954</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>578.2802096172716</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$87,A7,'Species'!$U$2:$U$87))</x:f>
-        <x:v>190804731.22600478</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.7118071430564346</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>514.9998980365926</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>169925263.72522268</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>20879467.500782102</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1228744157463555</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.12287441574635544</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>73471.96194647299</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5094568323320865</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>323.18919463276023</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>73471.96194647299</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>592.8683286875388</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$87,A8,'Species'!$U$2:$U$87))</x:f>
-        <x:v>43559199.28459989</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5094568323320865</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>323.18919463276023</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>23745344.209569413</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>19813855.07503048</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.8344311583845334</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.8344311583845334</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>50136.8501762255</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.652680666178162</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>449.44925633882144</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>50136.8501762255</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>489.8317072339797</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$87,A9,'Species'!$U$2:$U$87))</x:f>
-        <x:v>24558618.917154793</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.652680666178162</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>449.44925633882144</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>22533970.02687546</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2024648.890279334</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0898487433800883</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.08984874338008828</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>213.56844241209998</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.33087021231159</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2142.2502999521894</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>213.56844241209998</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2175.5683338552203</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$87,A10,'Species'!$U$2:$U$87))</x:f>
-        <x:v>464632.7404225469</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.33087021231159</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2142.2502999521894</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>457517.0598176431</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>7115.680604903842</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0155528202767783</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.015552820276778328</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R354a8d99f2e24df1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b8160069cf546e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7042,20 +6627,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7063,1146 +6638,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>253581.8995405308</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.820531302759516</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>661.5022150378653</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>253581.8995405308</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>661.7396459683708</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$87,A2,'Species'!$U$2:$U$87))</x:f>
-        <x:v>167805196.42593783</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.820531302759516</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>661.5022150378653</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>167744988.23957056</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>60208.18636727333</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0003589268865742</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00035892688657431014</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>11830.045580829501</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.056966484391215</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1140.1617949828426</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>11830.045580829501</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1240.3412228471818</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$87,A3,'Species'!$U$2:$U$87))</x:f>
-        <x:v>14673293.202063963</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.056966484391215</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1140.1617949828426</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>13488166.004167408</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1185127.197896555</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0878642209422977</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.08786422094229779</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>94.5926493338</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>94.5926493338</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$87,A4,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>206946.1681202048</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>206946.1681202048</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>60706.915371166004</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.9407097046435307</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>872.3880433231643</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>60706.915371166004</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>891.0129470437703</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$87,A5,'Species'!$U$2:$U$87))</x:f>
-        <x:v>54090647.57079938</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.9407097046435307</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>872.3880433231643</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>52959987.116836436</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1130660.4539629444</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0213493340069846</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.02134933400698464</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>627.2547708773001</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.888373866493557</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>773.3460408428679</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>627.2547708773001</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>773.8419728046546</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$87,A6,'Species'!$U$2:$U$87))</x:f>
-        <x:v>485396.06934682146</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.888373866493557</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>773.3460408428679</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>485084.9936577602</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>311.0756890612538</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0006412807922909</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.000641280792290857</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5349.284468381999</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.522257506203749</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>3328.5685559245085</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5349.284468381999</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>3341.542396405841</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$87,A7,'Species'!$U$2:$U$87))</x:f>
-        <x:v>17874860.84153373</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.522257506203749</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>3328.5685559245085</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>17805460.078151673</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>69400.76338205859</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.003897723680121</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.003897723680120871</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>42908.0999208108</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6100102544741155</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>407.3898968990061</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>42908.0999208108</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>407.43733039496686</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$87,A8,'Species'!$U$2:$U$87))</x:f>
-        <x:v>17482361.68405564</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6100102544741155</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>407.3898968990061</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>17480326.402871363</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2035.2811842784286</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0001164326762195</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.00011643267621959897</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>4034.7502554117004</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.0950372493240526</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1244.621358041666</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>4034.7502554117004</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1278.6189545133489</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$87,A9,'Species'!$U$2:$U$87))</x:f>
-        <x:v>5158908.153296975</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.0950372493240526</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1244.621358041666</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>5021736.34224947</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>137171.8110475056</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.027315613902991</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.02731561390299116</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2362.8067569799996</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.3011345302319293</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>20.00481457416732</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2362.8067569799996</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>20.018823859201486</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$87,A10,'Species'!$U$2:$U$87))</x:f>
-        <x:v>47300.612281313704</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.3011345302319293</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>20.00481457416732</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>47267.51104797451</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>33.10123333919182</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0007002956704363</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0007002956704362005</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1362.9277670796</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.27</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1862.0871366628655</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1362.9277670796</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1862.0871366628653</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$87,A11,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2537890.263279565</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.27</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1862.0871366628655</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>2537890.263279565</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>628896.889216885</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.154420542383399</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1426.9887273857746</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>628896.889216885</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1518.1591868901553</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$87,A12,'Species'!$U$2:$U$87))</x:f>
-        <x:v>954765589.9712541</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.154420542383399</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1426.9887273857746</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>897428771.6004752</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>57336818.37077892</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.063890104914426</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.06389010491442612</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>124094.87644476717</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.2994490484845005</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>199.2732704650601</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>124094.87644476717</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>232.23084012647416</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$87,A13,'Species'!$U$2:$U$87))</x:f>
-        <x:v>28818657.41215929</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.2994490484845005</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>199.2732704650601</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>24728791.877106305</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>4089865.535052985</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.1653888129827865</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.16538881298278651</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>91.87386681219999</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.004949694816575</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1011.4622878094386</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>91.87386681219999</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1518.7989755091594</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$87,A14,'Species'!$U$2:$U$87))</x:f>
-        <x:v>139537.93479043432</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.004949694816575</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1011.4622878094386</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>92926.95151576746</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>46610.983274666854</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.5015873491422786</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.5015873491422786</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>99.0000000021</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.53</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>33.88441561392024</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>99.0000000021</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$87,A15,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>3354.557145849261</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.53</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>3354.557145849261</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>23992.265780434</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>23992.265780434</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$87,A16,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>239922.65780434</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>239922.65780434</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>283848.87601948</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.200220557744029</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>15.856982895998412</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>283848.87601948</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>15.864048860387006</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$87,A17,'Species'!$U$2:$U$87))</x:f>
-        <x:v>4502992.438138965</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.200220557744029</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>15.856982895998412</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>4500986.772089268</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>2005.666049696505</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0004456058529507</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.00044560585295066644</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>579.4018725424</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>4.051341374329396</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>1125.4893098492282</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>579.4018725424</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>1762.5604961592346</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$87,A18,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1021230.8519439222</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>4.051341374329396</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>1125.4893098492282</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>652110.6136530964</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>369120.23829082586</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.5660393046250694</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.5660393046250692</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>7923.398566567</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.5146918505850433</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>32.710851586050985</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>7923.398566567</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>32.82610252088232</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$87,A19,'Species'!$U$2:$U$87))</x:f>
-        <x:v>260094.2936599404</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.5146918505850433</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>32.710851586050985</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>259181.11456810226</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>913.1790918381303</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.003523324194974</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.0035233241949740282</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>363.000000003</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>4.268539944902464</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>1855.8374950898676</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>363.000000003</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>2247.8299567951203</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$87,A20,'Species'!$U$2:$U$87))</x:f>
-        <x:v>815962.2743233722</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>4.268539944902464</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>1855.8374950898676</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>673669.0107231895</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>142293.26360018272</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.2112213287760256</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.21122132877602562</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>2831</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.59</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>389.04514499428046</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>2831</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>389.04514499428046</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$87,A21,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>1101386.805478808</x:v>
       </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.59</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>389.04514499428046</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>1101386.805478808</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R967eec859aca4b8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2dfc82e790e340d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8377,7 +7208,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8476,7 +7307,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1272031530.1874144</x:v>
+        <x:v>1165759568.7681806</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8490,7 +7321,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1272031530.1874144</x:v>
+        <x:v>1207458955.0805123</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8504,7 +7335,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-2.384185791015625e-7</x:v>
+        <x:v>-106271961.41923404</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8518,7 +7349,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-2.384185791015625e-7</x:v>
+        <x:v>-64572575.10690236</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8529,9 +7360,9 @@
         <x:v>EEZ_032</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8543,47 +7374,19 @@
         <x:v>EEZ_032</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_032</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_032</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74777d1e75a342f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8db897787364e14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8630,7 +7433,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
